--- a/verification/report-samples/monthly.xlsx
+++ b/verification/report-samples/monthly.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -23,10 +23,10 @@
     <t xml:space="preserve">test@example.test · TEST ·  · </t>
   </si>
   <si>
-    <t>TRANPORT MONTHLY HISSAB · TEST accounting period</t>
-  </si>
-  <si>
-    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-06T19:37:02.79+00:00</t>
+    <t>TRANSPORT MONTHLY ACCOUNT · TEST accounting period</t>
+  </si>
+  <si>
+    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-11T16:34:22.639+00:00</t>
   </si>
   <si>
     <t>INCOMPLETE — missing mappings/sources; review notes.</t>
@@ -47,13 +47,13 @@
     <t>INCOME</t>
   </si>
   <si>
-    <t>CHALLAN</t>
+    <t>Punjab Police</t>
   </si>
   <si>
     <t>TOLL PLAZA</t>
   </si>
   <si>
-    <t>DESEL</t>
+    <t>DIESEL</t>
   </si>
   <si>
     <t>GBT</t>
@@ -62,7 +62,7 @@
     <t>MONTH MAINT.</t>
   </si>
   <si>
-    <t>DRIVER. COMM.</t>
+    <t>DRIVER COMM.</t>
   </si>
   <si>
     <t>Last Main</t>
@@ -92,10 +92,10 @@
     <t>AVE</t>
   </si>
   <si>
-    <t>WEGHT</t>
-  </si>
-  <si>
-    <t>chaker</t>
+    <t>WEIGHT</t>
+  </si>
+  <si>
+    <t>CYCLES</t>
   </si>
   <si>
     <t>TEST-001</t>
@@ -133,7 +133,7 @@
     <t>TOTAL PROFIT/LOSS</t>
   </si>
   <si>
-    <t>SHARS</t>
+    <t>SHARES</t>
   </si>
   <si>
     <t>1 SHARE =</t>
@@ -160,12 +160,6 @@
     <t>Unavailable</t>
   </si>
   <si>
-    <t>MANAGER SIGN</t>
-  </si>
-  <si>
-    <t>C.E.O SIGN</t>
-  </si>
-  <si>
     <t>Canonical reconciliation (separate from unconfirmed printed subtotals)</t>
   </si>
   <si>
@@ -196,10 +190,21 @@
     <t>Printed final result</t>
   </si>
   <si>
+    <t>Manager signature</t>
+  </si>
+  <si>
+    <t>C.E.O. signature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature: __________________
+Name: ____________________
+Date: _____________________</t>
+  </si>
+  <si>
     <t>INCOME, Last Main, Total Main, MAIN, MIST, Total Sale and printed final PROFIT LOSS need confirmed business mappings. Percentages, shares, beneficiaries and comparison history are not configured; their slots remain blank.</t>
   </si>
   <si>
-    <t>DESEL before MONTH MAINT. is PKR cost; DESEL after KM is matched measured litres. AVE uses four decimals. Carried balances are not current expenses.</t>
+    <t>DIESEL before MONTH MAINT. is PKR cost; DIESEL after KM is matched measured litres. AVE uses four decimals. Carried balances are not current expenses.</t>
   </si>
 </sst>
 </file>
@@ -720,7 +725,7 @@
   <dimension ref="A1:CF33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="84" width="1.9" customWidth="1"/>
+    <col min="1" max="84" width="1.35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
@@ -2409,7 +2414,7 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2497,7 +2502,7 @@
     </row>
     <row r="25" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2507,7 +2512,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -2517,7 +2524,9 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
+      <c r="T25" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2526,7 +2535,9 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
+      <c r="AC25" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
@@ -2535,19 +2546,21 @@
       <c r="AI25" s="3"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
-      <c r="AL25" s="3"/>
+      <c r="AL25" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="AM25" s="3"/>
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-      <c r="AQ25" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="AQ25" s="3"/>
       <c r="AR25" s="3"/>
       <c r="AS25" s="3"/>
       <c r="AT25" s="3"/>
       <c r="AU25" s="3"/>
-      <c r="AV25" s="3"/>
+      <c r="AV25" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="AW25" s="3"/>
       <c r="AX25" s="3"/>
       <c r="AY25" s="3"/>
@@ -2556,7 +2569,9 @@
       <c r="BB25" s="3"/>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3"/>
-      <c r="BE25" s="3"/>
+      <c r="BE25" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="BF25" s="3"/>
       <c r="BG25" s="3"/>
       <c r="BH25" s="3"/>
@@ -2565,7 +2580,9 @@
       <c r="BK25" s="3"/>
       <c r="BL25" s="3"/>
       <c r="BM25" s="3"/>
-      <c r="BN25" s="3"/>
+      <c r="BN25" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
       <c r="BQ25" s="3"/>
@@ -2575,7 +2592,9 @@
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
       <c r="BW25" s="3"/>
-      <c r="BX25" s="3"/>
+      <c r="BX25" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="BY25" s="3"/>
       <c r="BZ25" s="3"/>
       <c r="CA25" s="3"/>
@@ -2585,95 +2604,109 @@
       <c r="CE25" s="3"/>
       <c r="CF25" s="3"/>
     </row>
-    <row r="26" ht="42" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
-      <c r="AB26" s="6"/>
-      <c r="AC26" s="6"/>
-      <c r="AD26" s="6"/>
-      <c r="AE26" s="6"/>
-      <c r="AF26" s="6"/>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="6"/>
-      <c r="AK26" s="6"/>
-      <c r="AL26" s="6"/>
-      <c r="AM26" s="6"/>
-      <c r="AN26" s="6"/>
-      <c r="AO26" s="6"/>
-      <c r="AP26" s="6"/>
-      <c r="AQ26" s="6"/>
-      <c r="AR26" s="6"/>
-      <c r="AS26" s="6"/>
-      <c r="AT26" s="6"/>
-      <c r="AU26" s="6"/>
-      <c r="AV26" s="6"/>
-      <c r="AW26" s="6"/>
-      <c r="AX26" s="6"/>
-      <c r="AY26" s="6"/>
-      <c r="AZ26" s="6"/>
-      <c r="BA26" s="6"/>
-      <c r="BB26" s="6"/>
-      <c r="BC26" s="6"/>
-      <c r="BD26" s="6"/>
-      <c r="BE26" s="6"/>
-      <c r="BF26" s="6"/>
-      <c r="BG26" s="6"/>
-      <c r="BH26" s="6"/>
-      <c r="BI26" s="6"/>
-      <c r="BJ26" s="6"/>
-      <c r="BK26" s="6"/>
-      <c r="BL26" s="6"/>
-      <c r="BM26" s="6"/>
-      <c r="BN26" s="6"/>
-      <c r="BO26" s="6"/>
-      <c r="BP26" s="6"/>
-      <c r="BQ26" s="6"/>
-      <c r="BR26" s="6"/>
-      <c r="BS26" s="6"/>
-      <c r="BT26" s="6"/>
-      <c r="BU26" s="6"/>
-      <c r="BV26" s="6"/>
-      <c r="BW26" s="6"/>
-      <c r="BX26" s="6"/>
-      <c r="BY26" s="6"/>
-      <c r="BZ26" s="6"/>
-      <c r="CA26" s="6"/>
-      <c r="CB26" s="6"/>
-      <c r="CC26" s="6"/>
-      <c r="CD26" s="6"/>
-      <c r="CE26" s="6"/>
-      <c r="CF26" s="6"/>
+    <row r="26" ht="24" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>80000</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7">
+        <v>36000</v>
+      </c>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="7">
+        <v>1800</v>
+      </c>
+      <c r="AD26" s="7"/>
+      <c r="AE26" s="7"/>
+      <c r="AF26" s="7"/>
+      <c r="AG26" s="7"/>
+      <c r="AH26" s="7"/>
+      <c r="AI26" s="7"/>
+      <c r="AJ26" s="7"/>
+      <c r="AK26" s="7"/>
+      <c r="AL26" s="7">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="7"/>
+      <c r="AN26" s="7"/>
+      <c r="AO26" s="7"/>
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="7"/>
+      <c r="AS26" s="7"/>
+      <c r="AT26" s="7"/>
+      <c r="AU26" s="7"/>
+      <c r="AV26" s="7">
+        <v>42200</v>
+      </c>
+      <c r="AW26" s="7"/>
+      <c r="AX26" s="7"/>
+      <c r="AY26" s="7"/>
+      <c r="AZ26" s="7"/>
+      <c r="BA26" s="7"/>
+      <c r="BB26" s="7"/>
+      <c r="BC26" s="7"/>
+      <c r="BD26" s="7"/>
+      <c r="BE26" s="7">
+        <v>44000</v>
+      </c>
+      <c r="BF26" s="7"/>
+      <c r="BG26" s="7"/>
+      <c r="BH26" s="7"/>
+      <c r="BI26" s="7"/>
+      <c r="BJ26" s="7"/>
+      <c r="BK26" s="7"/>
+      <c r="BL26" s="7"/>
+      <c r="BM26" s="7"/>
+      <c r="BN26" s="7"/>
+      <c r="BO26" s="7"/>
+      <c r="BP26" s="7"/>
+      <c r="BQ26" s="7"/>
+      <c r="BR26" s="7"/>
+      <c r="BS26" s="7"/>
+      <c r="BT26" s="7"/>
+      <c r="BU26" s="7"/>
+      <c r="BV26" s="7"/>
+      <c r="BW26" s="7"/>
+      <c r="BX26" s="7"/>
+      <c r="BY26" s="7"/>
+      <c r="BZ26" s="7"/>
+      <c r="CA26" s="7"/>
+      <c r="CB26" s="7"/>
+      <c r="CC26" s="7"/>
+      <c r="CD26" s="7"/>
+      <c r="CE26" s="7"/>
+      <c r="CF26" s="7"/>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2761,7 +2794,7 @@
     </row>
     <row r="29" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2771,9 +2804,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -2783,9 +2814,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
-      <c r="T29" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -2794,9 +2823,7 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
-      <c r="AC29" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
@@ -2805,21 +2832,19 @@
       <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
-      <c r="AL29" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
       <c r="AN29" s="3"/>
       <c r="AO29" s="3"/>
       <c r="AP29" s="3"/>
-      <c r="AQ29" s="3"/>
+      <c r="AQ29" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="AR29" s="3"/>
       <c r="AS29" s="3"/>
       <c r="AT29" s="3"/>
       <c r="AU29" s="3"/>
-      <c r="AV29" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="AV29" s="3"/>
       <c r="AW29" s="3"/>
       <c r="AX29" s="3"/>
       <c r="AY29" s="3"/>
@@ -2828,9 +2853,7 @@
       <c r="BB29" s="3"/>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3"/>
-      <c r="BE29" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="BE29" s="3"/>
       <c r="BF29" s="3"/>
       <c r="BG29" s="3"/>
       <c r="BH29" s="3"/>
@@ -2839,9 +2862,7 @@
       <c r="BK29" s="3"/>
       <c r="BL29" s="3"/>
       <c r="BM29" s="3"/>
-      <c r="BN29" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="BN29" s="3"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
       <c r="BQ29" s="3"/>
@@ -2851,9 +2872,7 @@
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
       <c r="BW29" s="3"/>
-      <c r="BX29" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="BX29" s="3"/>
       <c r="BY29" s="3"/>
       <c r="BZ29" s="3"/>
       <c r="CA29" s="3"/>
@@ -2863,109 +2882,99 @@
       <c r="CE29" s="3"/>
       <c r="CF29" s="3"/>
     </row>
-    <row r="30" ht="24" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>80000</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7">
-        <v>0</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7">
-        <v>36000</v>
-      </c>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="7"/>
-      <c r="AC30" s="7">
-        <v>1800</v>
-      </c>
-      <c r="AD30" s="7"/>
-      <c r="AE30" s="7"/>
-      <c r="AF30" s="7"/>
-      <c r="AG30" s="7"/>
-      <c r="AH30" s="7"/>
-      <c r="AI30" s="7"/>
-      <c r="AJ30" s="7"/>
-      <c r="AK30" s="7"/>
-      <c r="AL30" s="7">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="7"/>
-      <c r="AN30" s="7"/>
-      <c r="AO30" s="7"/>
-      <c r="AP30" s="7"/>
-      <c r="AQ30" s="7"/>
-      <c r="AR30" s="7"/>
-      <c r="AS30" s="7"/>
-      <c r="AT30" s="7"/>
-      <c r="AU30" s="7"/>
-      <c r="AV30" s="7">
-        <v>42200</v>
-      </c>
-      <c r="AW30" s="7"/>
-      <c r="AX30" s="7"/>
-      <c r="AY30" s="7"/>
-      <c r="AZ30" s="7"/>
-      <c r="BA30" s="7"/>
-      <c r="BB30" s="7"/>
-      <c r="BC30" s="7"/>
-      <c r="BD30" s="7"/>
-      <c r="BE30" s="7">
-        <v>44000</v>
-      </c>
-      <c r="BF30" s="7"/>
-      <c r="BG30" s="7"/>
-      <c r="BH30" s="7"/>
-      <c r="BI30" s="7"/>
-      <c r="BJ30" s="7"/>
-      <c r="BK30" s="7"/>
-      <c r="BL30" s="7"/>
-      <c r="BM30" s="7"/>
-      <c r="BN30" s="7"/>
-      <c r="BO30" s="7"/>
-      <c r="BP30" s="7"/>
-      <c r="BQ30" s="7"/>
-      <c r="BR30" s="7"/>
-      <c r="BS30" s="7"/>
-      <c r="BT30" s="7"/>
-      <c r="BU30" s="7"/>
-      <c r="BV30" s="7"/>
-      <c r="BW30" s="7"/>
-      <c r="BX30" s="7"/>
-      <c r="BY30" s="7"/>
-      <c r="BZ30" s="7"/>
-      <c r="CA30" s="7"/>
-      <c r="CB30" s="7"/>
-      <c r="CC30" s="7"/>
-      <c r="CD30" s="7"/>
-      <c r="CE30" s="7"/>
-      <c r="CF30" s="7"/>
+    <row r="30" ht="85" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="6"/>
+      <c r="AJ30" s="6"/>
+      <c r="AK30" s="6"/>
+      <c r="AL30" s="6"/>
+      <c r="AM30" s="6"/>
+      <c r="AN30" s="6"/>
+      <c r="AO30" s="6"/>
+      <c r="AP30" s="6"/>
+      <c r="AQ30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR30" s="6"/>
+      <c r="AS30" s="6"/>
+      <c r="AT30" s="6"/>
+      <c r="AU30" s="6"/>
+      <c r="AV30" s="6"/>
+      <c r="AW30" s="6"/>
+      <c r="AX30" s="6"/>
+      <c r="AY30" s="6"/>
+      <c r="AZ30" s="6"/>
+      <c r="BA30" s="6"/>
+      <c r="BB30" s="6"/>
+      <c r="BC30" s="6"/>
+      <c r="BD30" s="6"/>
+      <c r="BE30" s="6"/>
+      <c r="BF30" s="6"/>
+      <c r="BG30" s="6"/>
+      <c r="BH30" s="6"/>
+      <c r="BI30" s="6"/>
+      <c r="BJ30" s="6"/>
+      <c r="BK30" s="6"/>
+      <c r="BL30" s="6"/>
+      <c r="BM30" s="6"/>
+      <c r="BN30" s="6"/>
+      <c r="BO30" s="6"/>
+      <c r="BP30" s="6"/>
+      <c r="BQ30" s="6"/>
+      <c r="BR30" s="6"/>
+      <c r="BS30" s="6"/>
+      <c r="BT30" s="6"/>
+      <c r="BU30" s="6"/>
+      <c r="BV30" s="6"/>
+      <c r="BW30" s="6"/>
+      <c r="BX30" s="6"/>
+      <c r="BY30" s="6"/>
+      <c r="BZ30" s="6"/>
+      <c r="CA30" s="6"/>
+      <c r="CB30" s="6"/>
+      <c r="CC30" s="6"/>
+      <c r="CD30" s="6"/>
+      <c r="CE30" s="6"/>
+      <c r="CF30" s="6"/>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3053,7 +3062,7 @@
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3241,35 +3250,35 @@
     <mergeCell ref="AQ22:BK22"/>
     <mergeCell ref="BL22:CF22"/>
     <mergeCell ref="A24:CF24"/>
-    <mergeCell ref="A25:AP25"/>
-    <mergeCell ref="AQ25:CF25"/>
-    <mergeCell ref="A26:AP26"/>
-    <mergeCell ref="AQ26:CF26"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="J25:S25"/>
+    <mergeCell ref="T25:AB25"/>
+    <mergeCell ref="AC25:AK25"/>
+    <mergeCell ref="AL25:AU25"/>
+    <mergeCell ref="AV25:BD25"/>
+    <mergeCell ref="BE25:BM25"/>
+    <mergeCell ref="BN25:BW25"/>
+    <mergeCell ref="BX25:CF25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="J26:S26"/>
+    <mergeCell ref="T26:AB26"/>
+    <mergeCell ref="AC26:AK26"/>
+    <mergeCell ref="AL26:AU26"/>
+    <mergeCell ref="AV26:BD26"/>
+    <mergeCell ref="BE26:BM26"/>
+    <mergeCell ref="BN26:BW26"/>
+    <mergeCell ref="BX26:CF26"/>
     <mergeCell ref="A28:CF28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="J29:S29"/>
-    <mergeCell ref="T29:AB29"/>
-    <mergeCell ref="AC29:AK29"/>
-    <mergeCell ref="AL29:AU29"/>
-    <mergeCell ref="AV29:BD29"/>
-    <mergeCell ref="BE29:BM29"/>
-    <mergeCell ref="BN29:BW29"/>
-    <mergeCell ref="BX29:CF29"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="J30:S30"/>
-    <mergeCell ref="T30:AB30"/>
-    <mergeCell ref="AC30:AK30"/>
-    <mergeCell ref="AL30:AU30"/>
-    <mergeCell ref="AV30:BD30"/>
-    <mergeCell ref="BE30:BM30"/>
-    <mergeCell ref="BN30:BW30"/>
-    <mergeCell ref="BX30:CF30"/>
+    <mergeCell ref="A29:AP29"/>
+    <mergeCell ref="AQ29:CF29"/>
+    <mergeCell ref="A30:AP30"/>
+    <mergeCell ref="AQ30:CF30"/>
     <mergeCell ref="A32:CF32"/>
     <mergeCell ref="A33:CF33"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;LGujjar Brother Transport&amp;RPAGE &amp;P / &amp;N</oddFooter>
   </headerFooter>
